--- a/artfynd/A 17920-2023 artfynd.xlsx
+++ b/artfynd/A 17920-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 17920-2023 artfynd.xlsx
+++ b/artfynd/A 17920-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>72210181</v>
       </c>
       <c r="B2" t="n">
-        <v>57549</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -732,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>336129.7225984413</v>
+        <v>336130</v>
       </c>
       <c r="R2" t="n">
-        <v>6497829.306526847</v>
+        <v>6497829</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -765,19 +760,9 @@
           <t>2018-07-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-07-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
